--- a/Dosya_Durumlari.xlsx
+++ b/Dosya_Durumlari.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Dosya Durumları" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$57</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
   <si>
     <t>Tarih</t>
   </si>
@@ -331,6 +331,69 @@
   </si>
   <si>
     <t>18947/2024</t>
+  </si>
+  <si>
+    <t>15.06.2026</t>
+  </si>
+  <si>
+    <t>B.N.</t>
+  </si>
+  <si>
+    <t>16675/2022</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>U.G.</t>
+  </si>
+  <si>
+    <t>14051/2022</t>
+  </si>
+  <si>
+    <t>Y.M.</t>
+  </si>
+  <si>
+    <t>37947/2022</t>
+  </si>
+  <si>
+    <t>S.E.</t>
+  </si>
+  <si>
+    <t>12644/2024</t>
+  </si>
+  <si>
+    <t>I.E.</t>
+  </si>
+  <si>
+    <t>12926/2024</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>I.E</t>
+  </si>
+  <si>
+    <t>24988/2023</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>B.D.</t>
+  </si>
+  <si>
+    <t>16677/2022</t>
+  </si>
+  <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>C.S.</t>
+  </si>
+  <si>
+    <t>42146/2023</t>
   </si>
 </sst>
 </file>
@@ -712,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1407,8 +1470,120 @@
         <v>7</v>
       </c>
     </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D49"/>
+  <autoFilter ref="A1:D57"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dosya_Durumlari.xlsx
+++ b/Dosya_Durumlari.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Dosya Durumları" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$136</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="278">
   <si>
     <t>Tarih</t>
   </si>
@@ -394,6 +394,468 @@
   </si>
   <si>
     <t>42146/2023</t>
+  </si>
+  <si>
+    <t>29.04.2026</t>
+  </si>
+  <si>
+    <t>S.A</t>
+  </si>
+  <si>
+    <t>88098/2018</t>
+  </si>
+  <si>
+    <t>K.M</t>
+  </si>
+  <si>
+    <t>36894/2019</t>
+  </si>
+  <si>
+    <t>K.V</t>
+  </si>
+  <si>
+    <t>49302/2019</t>
+  </si>
+  <si>
+    <t>K.D</t>
+  </si>
+  <si>
+    <t>49305/2019</t>
+  </si>
+  <si>
+    <t>F.A</t>
+  </si>
+  <si>
+    <t>52528/2019</t>
+  </si>
+  <si>
+    <t>C.D</t>
+  </si>
+  <si>
+    <t>52532/2019</t>
+  </si>
+  <si>
+    <t>O.S</t>
+  </si>
+  <si>
+    <t>54990/2019</t>
+  </si>
+  <si>
+    <t>K.A</t>
+  </si>
+  <si>
+    <t>13156/2020</t>
+  </si>
+  <si>
+    <t>G.A</t>
+  </si>
+  <si>
+    <t>13158/2020</t>
+  </si>
+  <si>
+    <t>S.G</t>
+  </si>
+  <si>
+    <t>22038/2020</t>
+  </si>
+  <si>
+    <t>M.A</t>
+  </si>
+  <si>
+    <t>22041/2020</t>
+  </si>
+  <si>
+    <t>S.S</t>
+  </si>
+  <si>
+    <t>22042/2020</t>
+  </si>
+  <si>
+    <t>S.I</t>
+  </si>
+  <si>
+    <t>22045/2020</t>
+  </si>
+  <si>
+    <t>F.I</t>
+  </si>
+  <si>
+    <t>21170/2021</t>
+  </si>
+  <si>
+    <t>25819/2021</t>
+  </si>
+  <si>
+    <t>I.V</t>
+  </si>
+  <si>
+    <t>26131/2021</t>
+  </si>
+  <si>
+    <t>N.M</t>
+  </si>
+  <si>
+    <t>27105/2021</t>
+  </si>
+  <si>
+    <t>S.V</t>
+  </si>
+  <si>
+    <t>28432/2021</t>
+  </si>
+  <si>
+    <t>H.T</t>
+  </si>
+  <si>
+    <t>31427/2021</t>
+  </si>
+  <si>
+    <t>P.A</t>
+  </si>
+  <si>
+    <t>31429/2021</t>
+  </si>
+  <si>
+    <t>Y.K</t>
+  </si>
+  <si>
+    <t>32492/2021</t>
+  </si>
+  <si>
+    <t>L.O</t>
+  </si>
+  <si>
+    <t>33764/2021</t>
+  </si>
+  <si>
+    <t>S.T</t>
+  </si>
+  <si>
+    <t>34327/2021</t>
+  </si>
+  <si>
+    <t>B.I</t>
+  </si>
+  <si>
+    <t>35929/2021</t>
+  </si>
+  <si>
+    <t>I.G</t>
+  </si>
+  <si>
+    <t>36787/2021</t>
+  </si>
+  <si>
+    <t>36791/2021</t>
+  </si>
+  <si>
+    <t>C.A</t>
+  </si>
+  <si>
+    <t>36975/2021</t>
+  </si>
+  <si>
+    <t>T.B</t>
+  </si>
+  <si>
+    <t>41253/2021</t>
+  </si>
+  <si>
+    <t>T.I</t>
+  </si>
+  <si>
+    <t>41254/2021</t>
+  </si>
+  <si>
+    <t>L.A</t>
+  </si>
+  <si>
+    <t>41255/2021</t>
+  </si>
+  <si>
+    <t>M.M</t>
+  </si>
+  <si>
+    <t>41405/2021</t>
+  </si>
+  <si>
+    <t>V.V</t>
+  </si>
+  <si>
+    <t>41407/2021</t>
+  </si>
+  <si>
+    <t>M.V</t>
+  </si>
+  <si>
+    <t>41413/2021</t>
+  </si>
+  <si>
+    <t>42574/2021</t>
+  </si>
+  <si>
+    <t>T.A</t>
+  </si>
+  <si>
+    <t>44003/2021</t>
+  </si>
+  <si>
+    <t>44019/2021</t>
+  </si>
+  <si>
+    <t>B.N</t>
+  </si>
+  <si>
+    <t>44035/2021</t>
+  </si>
+  <si>
+    <t>R.O</t>
+  </si>
+  <si>
+    <t>44084/2021</t>
+  </si>
+  <si>
+    <t>D.Y</t>
+  </si>
+  <si>
+    <t>44914/2021</t>
+  </si>
+  <si>
+    <t>D.E</t>
+  </si>
+  <si>
+    <t>44915/2021</t>
+  </si>
+  <si>
+    <t>45746/2021</t>
+  </si>
+  <si>
+    <t>21.04.2026</t>
+  </si>
+  <si>
+    <t>N.S.</t>
+  </si>
+  <si>
+    <t>41154/2021</t>
+  </si>
+  <si>
+    <t>17.04.2026</t>
+  </si>
+  <si>
+    <t>Y.O.</t>
+  </si>
+  <si>
+    <t>32116/2022</t>
+  </si>
+  <si>
+    <t>16.04.2026</t>
+  </si>
+  <si>
+    <t>O.L.</t>
+  </si>
+  <si>
+    <t>35799/2023</t>
+  </si>
+  <si>
+    <t>12.03.2026</t>
+  </si>
+  <si>
+    <t>F.E.</t>
+  </si>
+  <si>
+    <t>21447/2019</t>
+  </si>
+  <si>
+    <t>Ș.V.</t>
+  </si>
+  <si>
+    <t>69463/2019</t>
+  </si>
+  <si>
+    <t>88732/2019</t>
+  </si>
+  <si>
+    <t>M.G.</t>
+  </si>
+  <si>
+    <t>88746/2019</t>
+  </si>
+  <si>
+    <t>M.N.</t>
+  </si>
+  <si>
+    <t>98263/2019</t>
+  </si>
+  <si>
+    <t>S.M.</t>
+  </si>
+  <si>
+    <t>3663/2021</t>
+  </si>
+  <si>
+    <t>Z.V.</t>
+  </si>
+  <si>
+    <t>3827/2021</t>
+  </si>
+  <si>
+    <t>D.M.</t>
+  </si>
+  <si>
+    <t>24983/2021</t>
+  </si>
+  <si>
+    <t>K.L.</t>
+  </si>
+  <si>
+    <t>26039/2021</t>
+  </si>
+  <si>
+    <t>K.E.</t>
+  </si>
+  <si>
+    <t>26040/2021</t>
+  </si>
+  <si>
+    <t>26047/2021</t>
+  </si>
+  <si>
+    <t>26052/2021</t>
+  </si>
+  <si>
+    <t>Y.Y.</t>
+  </si>
+  <si>
+    <t>26173/2021</t>
+  </si>
+  <si>
+    <t>N.V.</t>
+  </si>
+  <si>
+    <t>26176/2021</t>
+  </si>
+  <si>
+    <t>I.V.</t>
+  </si>
+  <si>
+    <t>27967/2021</t>
+  </si>
+  <si>
+    <t>V.S.</t>
+  </si>
+  <si>
+    <t>28860/2021</t>
+  </si>
+  <si>
+    <t>B.L.</t>
+  </si>
+  <si>
+    <t>29793/2021</t>
+  </si>
+  <si>
+    <t>30073/2021</t>
+  </si>
+  <si>
+    <t>T.H.</t>
+  </si>
+  <si>
+    <t>31364/2024</t>
+  </si>
+  <si>
+    <t>B.V.</t>
+  </si>
+  <si>
+    <t>32528/2021</t>
+  </si>
+  <si>
+    <t>N.A.</t>
+  </si>
+  <si>
+    <t>32649/2021</t>
+  </si>
+  <si>
+    <t>M.B.</t>
+  </si>
+  <si>
+    <t>35401/2021</t>
+  </si>
+  <si>
+    <t>M.S.</t>
+  </si>
+  <si>
+    <t>36129/2021</t>
+  </si>
+  <si>
+    <t>K.H.</t>
+  </si>
+  <si>
+    <t>37289/2021</t>
+  </si>
+  <si>
+    <t>S.L.</t>
+  </si>
+  <si>
+    <t>38300/2021</t>
+  </si>
+  <si>
+    <t>P.A.</t>
+  </si>
+  <si>
+    <t>38326/2021</t>
+  </si>
+  <si>
+    <t>I.T.</t>
+  </si>
+  <si>
+    <t>40349/2021</t>
+  </si>
+  <si>
+    <t>40354/2021</t>
+  </si>
+  <si>
+    <t>C.T.</t>
+  </si>
+  <si>
+    <t>42097/2021</t>
+  </si>
+  <si>
+    <t>P.I.</t>
+  </si>
+  <si>
+    <t>42098/2021</t>
+  </si>
+  <si>
+    <t>3260/2023</t>
+  </si>
+  <si>
+    <t>05.03.2026</t>
+  </si>
+  <si>
+    <t>F.P.</t>
+  </si>
+  <si>
+    <t>75463/2019</t>
+  </si>
+  <si>
+    <t>26.02.2026</t>
+  </si>
+  <si>
+    <t>K.V.</t>
+  </si>
+  <si>
+    <t>13790/2021</t>
+  </si>
+  <si>
+    <t>22246/2023</t>
+  </si>
+  <si>
+    <t>17.02.2026</t>
+  </si>
+  <si>
+    <t>L.A.</t>
+  </si>
+  <si>
+    <t>7706/2023</t>
   </si>
 </sst>
 </file>
@@ -775,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1582,8 +2044,1114 @@
         <v>7</v>
       </c>
     </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D57"/>
+  <autoFilter ref="A1:D136"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dosya_Durumlari.xlsx
+++ b/Dosya_Durumlari.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Dosya Durumları" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$138</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="280">
   <si>
     <t>Tarih</t>
   </si>
@@ -856,6 +856,12 @@
   </si>
   <si>
     <t>7706/2023</t>
+  </si>
+  <si>
+    <t>S.N.(C)</t>
+  </si>
+  <si>
+    <t>69707/2017</t>
   </si>
 </sst>
 </file>
@@ -875,6 +881,8 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="4">
@@ -924,7 +932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -933,6 +941,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1237,11 +1248,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="62" customWidth="1"/>
   </cols>
@@ -1261,1897 +1272,1917 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4">
+        <v>46252</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="D26" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="D28" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="D33" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="D34" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="D36" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="D40" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="D42" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="D43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="2" t="s">
+      <c r="D44" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="D45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="D46" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="D47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="D48" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="D49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="D50" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B52" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="D52" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="D54" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="D55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="D56" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="D57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B58" s="2" t="s">
+      <c r="D58" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B59" s="3" t="s">
+      <c r="D59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="D60" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="D61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="D62" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="D63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B64" s="2" t="s">
+      <c r="D64" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="D65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="D66" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67" s="3" t="s">
+      <c r="D67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B68" s="2" t="s">
+      <c r="D68" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="D69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B70" s="2" t="s">
+      <c r="D70" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B71" s="3" t="s">
+      <c r="D71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="D72" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" s="3" t="s">
+      <c r="D73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="D74" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="D75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B76" s="2" t="s">
+      <c r="D76" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B77" s="3" t="s">
+      <c r="D77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B78" s="2" t="s">
+      <c r="D78" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B79" s="3" t="s">
+      <c r="D79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B80" s="2" t="s">
+      <c r="D80" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="D81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="D82" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B83" s="3" t="s">
+      <c r="D83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B84" s="2" t="s">
+      <c r="D84" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B85" s="3" t="s">
+      <c r="D85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B86" s="2" t="s">
+      <c r="D86" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B87" s="3" t="s">
+      <c r="D87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B88" s="2" t="s">
+      <c r="D88" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B89" s="3" t="s">
+      <c r="D89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B90" s="2" t="s">
+      <c r="D90" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B91" s="3" t="s">
+      <c r="D91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B92" s="2" t="s">
+      <c r="D92" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93" s="3" t="s">
+      <c r="D93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B94" s="2" t="s">
+      <c r="D94" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="3" t="s">
+      <c r="D95" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B96" s="2" t="s">
+      <c r="D96" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B97" s="3" t="s">
+      <c r="D97" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B98" s="2" t="s">
+      <c r="D98" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+      <c r="D99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B100" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+      <c r="D100" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B101" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+      <c r="D101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B102" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
+      <c r="D102" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C103" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+      <c r="D103" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B104" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
+      <c r="D104" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B105" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+      <c r="D105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B106" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
+      <c r="D106" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+      <c r="D107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B108" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+      <c r="D108" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B109" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
+      <c r="D109" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B110" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+      <c r="D110" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+      <c r="D111" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B112" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+      <c r="D112" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
+      <c r="D113" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B114" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+      <c r="D114" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
+      <c r="D115" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B116" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C116" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+      <c r="D116" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+      <c r="D117" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B118" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
+      <c r="D118" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B119" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+      <c r="D119" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B120" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C120" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
+      <c r="D120" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B121" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C121" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
+      <c r="D121" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B122" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
+      <c r="D122" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B123" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+      <c r="D123" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B124" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+      <c r="D124" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B125" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+      <c r="D125" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B126" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C126" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
+      <c r="D126" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+      <c r="D127" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B128" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
+      <c r="D128" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B129" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+      <c r="D129" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B130" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C130" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
+      <c r="D130" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B131" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
+      <c r="D131" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B132" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="2" t="s">
+      <c r="D132" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B133" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
+      <c r="D133" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B134" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C134" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
+      <c r="D134" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B135" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
+      <c r="D135" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B136" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C136" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
+      <c r="D136" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B137" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D137" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D136"/>
+  <autoFilter ref="A1:D138"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dosya_Durumlari.xlsx
+++ b/Dosya_Durumlari.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="283">
   <si>
     <t>Tarih</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Eksik Evrak / Doldurulacak Belgeler (Acte în completare)</t>
-  </si>
-  <si>
-    <t>18.08.2026</t>
   </si>
   <si>
     <t>S.N.(C)</t>
@@ -942,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -951,6 +948,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1293,14 +1293,14 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4">
+        <v>46253</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
@@ -1308,13 +1308,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
@@ -1322,13 +1322,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
@@ -1336,13 +1336,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>7</v>
@@ -1364,13 +1364,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
@@ -1378,13 +1378,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>7</v>
@@ -1392,13 +1392,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -1406,13 +1406,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>7</v>
@@ -1420,13 +1420,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
@@ -1434,13 +1434,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>7</v>
@@ -1448,13 +1448,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -1462,13 +1462,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>7</v>
@@ -1476,13 +1476,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
@@ -1490,13 +1490,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>7</v>
@@ -1504,13 +1504,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -1518,13 +1518,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>7</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
@@ -1546,13 +1546,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>7</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1574,13 +1574,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>7</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>7</v>
@@ -1602,13 +1602,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>7</v>
@@ -1616,13 +1616,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
@@ -1630,13 +1630,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>7</v>
@@ -1644,13 +1644,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -1658,13 +1658,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>7</v>
@@ -1672,13 +1672,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>7</v>
@@ -1686,13 +1686,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>7</v>
@@ -1700,13 +1700,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
@@ -1714,13 +1714,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>7</v>
@@ -1728,13 +1728,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
@@ -1742,13 +1742,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>7</v>
@@ -1756,13 +1756,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>7</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>7</v>
@@ -1784,13 +1784,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -1798,13 +1798,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>7</v>
@@ -1812,13 +1812,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>7</v>
@@ -1826,13 +1826,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>7</v>
@@ -1840,13 +1840,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>7</v>
@@ -1854,13 +1854,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>7</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>7</v>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>7</v>
@@ -1896,13 +1896,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>7</v>
@@ -1924,13 +1924,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>7</v>
@@ -1938,13 +1938,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>7</v>
@@ -1952,13 +1952,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>7</v>
@@ -1966,13 +1966,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>7</v>
@@ -1980,13 +1980,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>7</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>7</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
@@ -2022,13 +2022,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>7</v>
@@ -2036,13 +2036,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>7</v>
@@ -2050,13 +2050,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>7</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>7</v>
@@ -2078,13 +2078,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>7</v>
@@ -2092,13 +2092,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>7</v>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>7</v>
@@ -2120,13 +2120,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>7</v>
@@ -2134,13 +2134,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>7</v>
@@ -2148,13 +2148,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>7</v>
@@ -2162,13 +2162,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>7</v>
@@ -2176,13 +2176,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>7</v>
@@ -2190,13 +2190,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>7</v>
@@ -2204,13 +2204,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -2218,13 +2218,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>7</v>
@@ -2232,13 +2232,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>7</v>
@@ -2260,13 +2260,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>7</v>
@@ -2274,13 +2274,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>7</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>7</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>7</v>
@@ -2316,13 +2316,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>7</v>
@@ -2330,13 +2330,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>7</v>
@@ -2344,13 +2344,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>7</v>
@@ -2358,13 +2358,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>7</v>
@@ -2372,13 +2372,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>7</v>
@@ -2386,13 +2386,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>7</v>
@@ -2400,13 +2400,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>7</v>
@@ -2414,13 +2414,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>7</v>
@@ -2428,13 +2428,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>7</v>
@@ -2442,13 +2442,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>7</v>
@@ -2456,13 +2456,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>7</v>
@@ -2470,13 +2470,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>7</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>7</v>
@@ -2498,13 +2498,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>7</v>
@@ -2512,13 +2512,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>7</v>
@@ -2526,13 +2526,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>7</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>7</v>
@@ -2554,13 +2554,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>7</v>
@@ -2568,13 +2568,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>7</v>
@@ -2582,13 +2582,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>7</v>
@@ -2596,13 +2596,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>7</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>7</v>
@@ -2624,13 +2624,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>7</v>
@@ -2638,13 +2638,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>7</v>
@@ -2652,13 +2652,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
@@ -2666,13 +2666,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>7</v>
@@ -2680,13 +2680,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>7</v>
@@ -2694,13 +2694,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>7</v>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>7</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>7</v>
@@ -2736,13 +2736,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>7</v>
@@ -2750,13 +2750,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>7</v>
@@ -2764,13 +2764,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>7</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>7</v>
@@ -2792,13 +2792,13 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -2806,13 +2806,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>7</v>
@@ -2820,13 +2820,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -2834,13 +2834,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>7</v>
@@ -2848,13 +2848,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>7</v>
@@ -2862,13 +2862,13 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>7</v>
@@ -2876,13 +2876,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>7</v>
@@ -2890,13 +2890,13 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>7</v>
@@ -2904,13 +2904,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -2918,13 +2918,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>7</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>7</v>
@@ -2946,13 +2946,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>7</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>7</v>
@@ -2974,13 +2974,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>7</v>
@@ -2988,13 +2988,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>7</v>
@@ -3002,13 +3002,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>7</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>7</v>
@@ -3030,13 +3030,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>7</v>
@@ -3044,13 +3044,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -3058,13 +3058,13 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>265</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>7</v>
@@ -3072,13 +3072,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>7</v>
@@ -3086,13 +3086,13 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>7</v>
@@ -3100,13 +3100,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -3114,13 +3114,13 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>7</v>
@@ -3128,13 +3128,13 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>7</v>
@@ -3142,13 +3142,13 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="C135" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>7</v>
@@ -3156,13 +3156,13 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>7</v>
@@ -3170,13 +3170,13 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>7</v>
@@ -3184,13 +3184,13 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>7</v>

--- a/Dosya_Durumlari.xlsx
+++ b/Dosya_Durumlari.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Dosya Durumları" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dosya Durumları'!$A$1:$D$160</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="322">
   <si>
     <t>Tarih</t>
   </si>
@@ -36,22 +36,130 @@
     <t>Doldurulacak Belgeler</t>
   </si>
   <si>
+    <t>31.08.2026</t>
+  </si>
+  <si>
+    <t>R.A.</t>
+  </si>
+  <si>
+    <t>27997/2023</t>
+  </si>
+  <si>
+    <t>Eksik Evrak / Doldurulacak Belgeler (Acte în completare)</t>
+  </si>
+  <si>
     <t>26.08.2026</t>
   </si>
   <si>
+    <t>S.I.</t>
+  </si>
+  <si>
+    <t>36347/2021</t>
+  </si>
+  <si>
+    <t>T.N. (B.)</t>
+  </si>
+  <si>
+    <t>37174/2021</t>
+  </si>
+  <si>
+    <t>M.M.</t>
+  </si>
+  <si>
+    <t>34646/2021</t>
+  </si>
+  <si>
+    <t>34661/2021</t>
+  </si>
+  <si>
+    <t>V.O.</t>
+  </si>
+  <si>
+    <t>34673/2021</t>
+  </si>
+  <si>
+    <t>H.Y.</t>
+  </si>
+  <si>
+    <t>34684/2021</t>
+  </si>
+  <si>
+    <t>M.V. (Ș.)</t>
+  </si>
+  <si>
+    <t>36326/2021</t>
+  </si>
+  <si>
+    <t>B.V.</t>
+  </si>
+  <si>
+    <t>36332/2021</t>
+  </si>
+  <si>
+    <t>Z.Y.</t>
+  </si>
+  <si>
+    <t>36342/2021</t>
+  </si>
+  <si>
+    <t>V.V.</t>
+  </si>
+  <si>
+    <t>36344/2021</t>
+  </si>
+  <si>
     <t>A.R.</t>
   </si>
   <si>
     <t>14668/2023</t>
   </si>
   <si>
-    <t>Eksik Evrak / Doldurulacak Belgeler (Acte în completare)</t>
-  </si>
-  <si>
-    <t>T.N. (B.)</t>
-  </si>
-  <si>
-    <t>37174/2021</t>
+    <t>I.O.</t>
+  </si>
+  <si>
+    <t>19023/2024</t>
+  </si>
+  <si>
+    <t>S.O.</t>
+  </si>
+  <si>
+    <t>37199/2021</t>
+  </si>
+  <si>
+    <t>T.R.</t>
+  </si>
+  <si>
+    <t>37205/2021</t>
+  </si>
+  <si>
+    <t>M.I.</t>
+  </si>
+  <si>
+    <t>37206/2021</t>
+  </si>
+  <si>
+    <t>37208/2021</t>
+  </si>
+  <si>
+    <t>M.A.</t>
+  </si>
+  <si>
+    <t>37225/2021</t>
+  </si>
+  <si>
+    <t>R.O.</t>
+  </si>
+  <si>
+    <t>40320/2021</t>
+  </si>
+  <si>
+    <t>40325/2021</t>
+  </si>
+  <si>
+    <t>T.S.</t>
+  </si>
+  <si>
+    <t>34629/2021</t>
   </si>
   <si>
     <t>B.P.</t>
@@ -60,105 +168,6 @@
     <t>32512/2021</t>
   </si>
   <si>
-    <t>T.S.</t>
-  </si>
-  <si>
-    <t>34629/2021</t>
-  </si>
-  <si>
-    <t>R.O.</t>
-  </si>
-  <si>
-    <t>40325/2021</t>
-  </si>
-  <si>
-    <t>40320/2021</t>
-  </si>
-  <si>
-    <t>M.A.</t>
-  </si>
-  <si>
-    <t>37225/2021</t>
-  </si>
-  <si>
-    <t>M.I.</t>
-  </si>
-  <si>
-    <t>37208/2021</t>
-  </si>
-  <si>
-    <t>37206/2021</t>
-  </si>
-  <si>
-    <t>T.R.</t>
-  </si>
-  <si>
-    <t>37205/2021</t>
-  </si>
-  <si>
-    <t>S.O.</t>
-  </si>
-  <si>
-    <t>37199/2021</t>
-  </si>
-  <si>
-    <t>I.O.</t>
-  </si>
-  <si>
-    <t>19023/2024</t>
-  </si>
-  <si>
-    <t>S.I.</t>
-  </si>
-  <si>
-    <t>36347/2021</t>
-  </si>
-  <si>
-    <t>V.V.</t>
-  </si>
-  <si>
-    <t>36344/2021</t>
-  </si>
-  <si>
-    <t>Z.Y.</t>
-  </si>
-  <si>
-    <t>36342/2021</t>
-  </si>
-  <si>
-    <t>B.V.</t>
-  </si>
-  <si>
-    <t>36332/2021</t>
-  </si>
-  <si>
-    <t>M.V. (Ș.)</t>
-  </si>
-  <si>
-    <t>36326/2021</t>
-  </si>
-  <si>
-    <t>H.Y.</t>
-  </si>
-  <si>
-    <t>34684/2021</t>
-  </si>
-  <si>
-    <t>V.O.</t>
-  </si>
-  <si>
-    <t>34673/2021</t>
-  </si>
-  <si>
-    <t>M.M.</t>
-  </si>
-  <si>
-    <t>34661/2021</t>
-  </si>
-  <si>
-    <t>34646/2021</t>
-  </si>
-  <si>
     <t>25.08.2026</t>
   </si>
   <si>
@@ -189,64 +198,196 @@
     <t>04.08.2026</t>
   </si>
   <si>
+    <t>G.M.</t>
+  </si>
+  <si>
+    <t>36351/2021</t>
+  </si>
+  <si>
+    <t>D.V.</t>
+  </si>
+  <si>
+    <t>65490/2019</t>
+  </si>
+  <si>
+    <t>P.V.</t>
+  </si>
+  <si>
+    <t>40367/2021</t>
+  </si>
+  <si>
+    <t>S.T.</t>
+  </si>
+  <si>
+    <t>36071/2021</t>
+  </si>
+  <si>
+    <t>K.I.</t>
+  </si>
+  <si>
+    <t>36076/2021</t>
+  </si>
+  <si>
+    <t>B.A.</t>
+  </si>
+  <si>
+    <t>36077/2021</t>
+  </si>
+  <si>
+    <t>B.M.</t>
+  </si>
+  <si>
+    <t>36339/2021</t>
+  </si>
+  <si>
+    <t>N.R.</t>
+  </si>
+  <si>
+    <t>36356/2021</t>
+  </si>
+  <si>
+    <t>10262/2024</t>
+  </si>
+  <si>
+    <t>M.R.</t>
+  </si>
+  <si>
+    <t>41322/2021</t>
+  </si>
+  <si>
+    <t>P.T.</t>
+  </si>
+  <si>
+    <t>42944/2021</t>
+  </si>
+  <si>
+    <t>Z.S.</t>
+  </si>
+  <si>
+    <t>52529/2019</t>
+  </si>
+  <si>
+    <t>K.M.</t>
+  </si>
+  <si>
+    <t>41307/2021</t>
+  </si>
+  <si>
+    <t>L.I.</t>
+  </si>
+  <si>
+    <t>17415/2023</t>
+  </si>
+  <si>
+    <t>L.N.</t>
+  </si>
+  <si>
+    <t>17419/2023</t>
+  </si>
+  <si>
+    <t>K.O.</t>
+  </si>
+  <si>
+    <t>42942/2021</t>
+  </si>
+  <si>
+    <t>P.K.</t>
+  </si>
+  <si>
+    <t>88654/2019</t>
+  </si>
+  <si>
+    <t>K.D.</t>
+  </si>
+  <si>
+    <t>34682/2021</t>
+  </si>
+  <si>
+    <t>S.A.</t>
+  </si>
+  <si>
+    <t>38294/2021</t>
+  </si>
+  <si>
+    <t>S.K.</t>
+  </si>
+  <si>
+    <t>34331/2021</t>
+  </si>
+  <si>
+    <t>K.A.</t>
+  </si>
+  <si>
+    <t>37234/2021</t>
+  </si>
+  <si>
+    <t>K.S.</t>
+  </si>
+  <si>
+    <t>18616/2020</t>
+  </si>
+  <si>
+    <t>O.I.</t>
+  </si>
+  <si>
+    <t>25004/2021</t>
+  </si>
+  <si>
+    <t>B.H.</t>
+  </si>
+  <si>
+    <t>25789/2021</t>
+  </si>
+  <si>
+    <t>25005/2021</t>
+  </si>
+  <si>
+    <t>13950/2021</t>
+  </si>
+  <si>
+    <t>15935/2021</t>
+  </si>
+  <si>
+    <t>1312/2021</t>
+  </si>
+  <si>
+    <t>P.M.</t>
+  </si>
+  <si>
+    <t>88655/2019</t>
+  </si>
+  <si>
+    <t>F.S.</t>
+  </si>
+  <si>
+    <t>28150/2021</t>
+  </si>
+  <si>
+    <t>R.D.</t>
+  </si>
+  <si>
+    <t>15957/2021</t>
+  </si>
+  <si>
+    <t>18617/2020</t>
+  </si>
+  <si>
     <t>T.N.</t>
   </si>
   <si>
     <t>17714/2020</t>
   </si>
   <si>
-    <t>B.H.</t>
-  </si>
-  <si>
-    <t>25789/2021</t>
-  </si>
-  <si>
-    <t>K.O.</t>
-  </si>
-  <si>
-    <t>25005/2021</t>
-  </si>
-  <si>
-    <t>13950/2021</t>
-  </si>
-  <si>
-    <t>15935/2021</t>
-  </si>
-  <si>
-    <t>R.A.</t>
-  </si>
-  <si>
-    <t>1312/2021</t>
-  </si>
-  <si>
-    <t>P.M.</t>
-  </si>
-  <si>
-    <t>88655/2019</t>
-  </si>
-  <si>
-    <t>K.A.</t>
-  </si>
-  <si>
-    <t>18617/2020</t>
-  </si>
-  <si>
-    <t>F.S.</t>
-  </si>
-  <si>
-    <t>28150/2021</t>
-  </si>
-  <si>
-    <t>R.D.</t>
-  </si>
-  <si>
-    <t>15957/2021</t>
-  </si>
-  <si>
-    <t>O.I.</t>
-  </si>
-  <si>
-    <t>25004/2021</t>
+    <t>C.E.</t>
+  </si>
+  <si>
+    <t>33833/2021</t>
+  </si>
+  <si>
+    <t>C.V.</t>
+  </si>
+  <si>
+    <t>30043/2021</t>
   </si>
   <si>
     <t>D.D.</t>
@@ -255,174 +396,39 @@
     <t>34342/2021</t>
   </si>
   <si>
+    <t>U.L.</t>
+  </si>
+  <si>
+    <t>29195/2021</t>
+  </si>
+  <si>
+    <t>Z.D.</t>
+  </si>
+  <si>
+    <t>31446/2021</t>
+  </si>
+  <si>
+    <t>R.I.</t>
+  </si>
+  <si>
+    <t>27117/2021</t>
+  </si>
+  <si>
+    <t>T.E.</t>
+  </si>
+  <si>
+    <t>36069/2021</t>
+  </si>
+  <si>
     <t>16570/2023</t>
   </si>
   <si>
-    <t>T.E.</t>
-  </si>
-  <si>
-    <t>36069/2021</t>
-  </si>
-  <si>
-    <t>R.I.</t>
-  </si>
-  <si>
-    <t>27117/2021</t>
-  </si>
-  <si>
-    <t>C.E.</t>
-  </si>
-  <si>
-    <t>33833/2021</t>
-  </si>
-  <si>
-    <t>U.L.</t>
-  </si>
-  <si>
-    <t>29195/2021</t>
-  </si>
-  <si>
-    <t>Z.D.</t>
-  </si>
-  <si>
-    <t>31446/2021</t>
-  </si>
-  <si>
-    <t>C.V.</t>
-  </si>
-  <si>
-    <t>30043/2021</t>
-  </si>
-  <si>
     <t>H.V.</t>
   </si>
   <si>
     <t>18626/2020</t>
   </si>
   <si>
-    <t>K.S.</t>
-  </si>
-  <si>
-    <t>18616/2020</t>
-  </si>
-  <si>
-    <t>P.K.</t>
-  </si>
-  <si>
-    <t>88654/2019</t>
-  </si>
-  <si>
-    <t>S.K.</t>
-  </si>
-  <si>
-    <t>34331/2021</t>
-  </si>
-  <si>
-    <t>D.V.</t>
-  </si>
-  <si>
-    <t>65490/2019</t>
-  </si>
-  <si>
-    <t>P.V.</t>
-  </si>
-  <si>
-    <t>40367/2021</t>
-  </si>
-  <si>
-    <t>S.T.</t>
-  </si>
-  <si>
-    <t>36071/2021</t>
-  </si>
-  <si>
-    <t>K.I.</t>
-  </si>
-  <si>
-    <t>36076/2021</t>
-  </si>
-  <si>
-    <t>B.A.</t>
-  </si>
-  <si>
-    <t>36077/2021</t>
-  </si>
-  <si>
-    <t>B.M.</t>
-  </si>
-  <si>
-    <t>36339/2021</t>
-  </si>
-  <si>
-    <t>N.R.</t>
-  </si>
-  <si>
-    <t>36356/2021</t>
-  </si>
-  <si>
-    <t>10262/2024</t>
-  </si>
-  <si>
-    <t>G.M.</t>
-  </si>
-  <si>
-    <t>36351/2021</t>
-  </si>
-  <si>
-    <t>37234/2021</t>
-  </si>
-  <si>
-    <t>P.T.</t>
-  </si>
-  <si>
-    <t>42944/2021</t>
-  </si>
-  <si>
-    <t>Z.S.</t>
-  </si>
-  <si>
-    <t>52529/2019</t>
-  </si>
-  <si>
-    <t>K.M.</t>
-  </si>
-  <si>
-    <t>41307/2021</t>
-  </si>
-  <si>
-    <t>L.I.</t>
-  </si>
-  <si>
-    <t>17415/2023</t>
-  </si>
-  <si>
-    <t>L.N.</t>
-  </si>
-  <si>
-    <t>17419/2023</t>
-  </si>
-  <si>
-    <t>42942/2021</t>
-  </si>
-  <si>
-    <t>M.R.</t>
-  </si>
-  <si>
-    <t>41322/2021</t>
-  </si>
-  <si>
-    <t>K.D.</t>
-  </si>
-  <si>
-    <t>34682/2021</t>
-  </si>
-  <si>
-    <t>S.A.</t>
-  </si>
-  <si>
-    <t>38294/2021</t>
-  </si>
-  <si>
     <t>03.08.2026</t>
   </si>
   <si>
@@ -474,30 +480,30 @@
     <t>20.05.2026</t>
   </si>
   <si>
+    <t>Y.M.</t>
+  </si>
+  <si>
+    <t>37947/2022</t>
+  </si>
+  <si>
+    <t>S.E.</t>
+  </si>
+  <si>
+    <t>12644/2024</t>
+  </si>
+  <si>
+    <t>U.G.</t>
+  </si>
+  <si>
+    <t>14051/2022</t>
+  </si>
+  <si>
     <t>I.E.</t>
   </si>
   <si>
     <t>12926/2024</t>
   </si>
   <si>
-    <t>S.E.</t>
-  </si>
-  <si>
-    <t>12644/2024</t>
-  </si>
-  <si>
-    <t>U.G.</t>
-  </si>
-  <si>
-    <t>14051/2022</t>
-  </si>
-  <si>
-    <t>Y.M.</t>
-  </si>
-  <si>
-    <t>37947/2022</t>
-  </si>
-  <si>
     <t>18.05.2026</t>
   </si>
   <si>
@@ -528,66 +534,189 @@
     <t>29.04.2026</t>
   </si>
   <si>
+    <t>S.S</t>
+  </si>
+  <si>
+    <t>22042/2020</t>
+  </si>
+  <si>
+    <t>T.A</t>
+  </si>
+  <si>
+    <t>44003/2021</t>
+  </si>
+  <si>
+    <t>K.A</t>
+  </si>
+  <si>
+    <t>13156/2020</t>
+  </si>
+  <si>
+    <t>I.V</t>
+  </si>
+  <si>
+    <t>26131/2021</t>
+  </si>
+  <si>
+    <t>H.T</t>
+  </si>
+  <si>
+    <t>31427/2021</t>
+  </si>
+  <si>
+    <t>S.V</t>
+  </si>
+  <si>
+    <t>28432/2021</t>
+  </si>
+  <si>
+    <t>P.A</t>
+  </si>
+  <si>
+    <t>31429/2021</t>
+  </si>
+  <si>
+    <t>M.A</t>
+  </si>
+  <si>
+    <t>22041/2020</t>
+  </si>
+  <si>
+    <t>S.G</t>
+  </si>
+  <si>
+    <t>22038/2020</t>
+  </si>
+  <si>
+    <t>V.V</t>
+  </si>
+  <si>
+    <t>41407/2021</t>
+  </si>
+  <si>
+    <t>S.I</t>
+  </si>
+  <si>
+    <t>22045/2020</t>
+  </si>
+  <si>
+    <t>O.S</t>
+  </si>
+  <si>
+    <t>54990/2019</t>
+  </si>
+  <si>
+    <t>D.E</t>
+  </si>
+  <si>
+    <t>45746/2021</t>
+  </si>
+  <si>
+    <t>42574/2021</t>
+  </si>
+  <si>
+    <t>44915/2021</t>
+  </si>
+  <si>
+    <t>D.Y</t>
+  </si>
+  <si>
+    <t>44914/2021</t>
+  </si>
+  <si>
+    <t>R.O</t>
+  </si>
+  <si>
+    <t>44084/2021</t>
+  </si>
+  <si>
+    <t>B.N</t>
+  </si>
+  <si>
+    <t>44035/2021</t>
+  </si>
+  <si>
+    <t>S.A</t>
+  </si>
+  <si>
+    <t>44019/2021</t>
+  </si>
+  <si>
+    <t>F.I</t>
+  </si>
+  <si>
+    <t>21170/2021</t>
+  </si>
+  <si>
+    <t>36791/2021</t>
+  </si>
+  <si>
+    <t>N.M</t>
+  </si>
+  <si>
+    <t>27105/2021</t>
+  </si>
+  <si>
+    <t>K.D</t>
+  </si>
+  <si>
+    <t>49305/2019</t>
+  </si>
+  <si>
+    <t>C.D</t>
+  </si>
+  <si>
+    <t>52532/2019</t>
+  </si>
+  <si>
+    <t>L.A</t>
+  </si>
+  <si>
+    <t>41255/2021</t>
+  </si>
+  <si>
+    <t>S.T</t>
+  </si>
+  <si>
+    <t>34327/2021</t>
+  </si>
+  <si>
+    <t>T.I</t>
+  </si>
+  <si>
+    <t>41254/2021</t>
+  </si>
+  <si>
+    <t>T.B</t>
+  </si>
+  <si>
+    <t>41253/2021</t>
+  </si>
+  <si>
+    <t>C.A</t>
+  </si>
+  <si>
+    <t>36975/2021</t>
+  </si>
+  <si>
+    <t>I.G</t>
+  </si>
+  <si>
+    <t>36787/2021</t>
+  </si>
+  <si>
+    <t>M.M</t>
+  </si>
+  <si>
+    <t>41405/2021</t>
+  </si>
+  <si>
     <t>B.I</t>
   </si>
   <si>
     <t>35929/2021</t>
   </si>
   <si>
-    <t>L.A</t>
-  </si>
-  <si>
-    <t>41255/2021</t>
-  </si>
-  <si>
-    <t>S.T</t>
-  </si>
-  <si>
-    <t>34327/2021</t>
-  </si>
-  <si>
-    <t>T.I</t>
-  </si>
-  <si>
-    <t>41254/2021</t>
-  </si>
-  <si>
-    <t>T.B</t>
-  </si>
-  <si>
-    <t>41253/2021</t>
-  </si>
-  <si>
-    <t>C.A</t>
-  </si>
-  <si>
-    <t>36975/2021</t>
-  </si>
-  <si>
-    <t>S.S</t>
-  </si>
-  <si>
-    <t>36791/2021</t>
-  </si>
-  <si>
-    <t>I.G</t>
-  </si>
-  <si>
-    <t>36787/2021</t>
-  </si>
-  <si>
-    <t>M.M</t>
-  </si>
-  <si>
-    <t>41405/2021</t>
-  </si>
-  <si>
-    <t>K.D</t>
-  </si>
-  <si>
-    <t>49305/2019</t>
-  </si>
-  <si>
     <t>L.O</t>
   </si>
   <si>
@@ -624,9 +753,6 @@
     <t>32492/2021</t>
   </si>
   <si>
-    <t>S.A</t>
-  </si>
-  <si>
     <t>88098/2018</t>
   </si>
   <si>
@@ -639,126 +765,6 @@
     <t>25819/2021</t>
   </si>
   <si>
-    <t>C.D</t>
-  </si>
-  <si>
-    <t>52532/2019</t>
-  </si>
-  <si>
-    <t>N.M</t>
-  </si>
-  <si>
-    <t>27105/2021</t>
-  </si>
-  <si>
-    <t>S.I</t>
-  </si>
-  <si>
-    <t>42574/2021</t>
-  </si>
-  <si>
-    <t>F.I</t>
-  </si>
-  <si>
-    <t>21170/2021</t>
-  </si>
-  <si>
-    <t>T.A</t>
-  </si>
-  <si>
-    <t>44003/2021</t>
-  </si>
-  <si>
-    <t>K.A</t>
-  </si>
-  <si>
-    <t>13156/2020</t>
-  </si>
-  <si>
-    <t>I.V</t>
-  </si>
-  <si>
-    <t>26131/2021</t>
-  </si>
-  <si>
-    <t>H.T</t>
-  </si>
-  <si>
-    <t>31427/2021</t>
-  </si>
-  <si>
-    <t>S.V</t>
-  </si>
-  <si>
-    <t>28432/2021</t>
-  </si>
-  <si>
-    <t>P.A</t>
-  </si>
-  <si>
-    <t>31429/2021</t>
-  </si>
-  <si>
-    <t>M.A</t>
-  </si>
-  <si>
-    <t>22041/2020</t>
-  </si>
-  <si>
-    <t>S.G</t>
-  </si>
-  <si>
-    <t>22038/2020</t>
-  </si>
-  <si>
-    <t>22042/2020</t>
-  </si>
-  <si>
-    <t>22045/2020</t>
-  </si>
-  <si>
-    <t>O.S</t>
-  </si>
-  <si>
-    <t>54990/2019</t>
-  </si>
-  <si>
-    <t>V.V</t>
-  </si>
-  <si>
-    <t>41407/2021</t>
-  </si>
-  <si>
-    <t>D.E</t>
-  </si>
-  <si>
-    <t>45746/2021</t>
-  </si>
-  <si>
-    <t>44915/2021</t>
-  </si>
-  <si>
-    <t>D.Y</t>
-  </si>
-  <si>
-    <t>44914/2021</t>
-  </si>
-  <si>
-    <t>R.O</t>
-  </si>
-  <si>
-    <t>44084/2021</t>
-  </si>
-  <si>
-    <t>B.N</t>
-  </si>
-  <si>
-    <t>44035/2021</t>
-  </si>
-  <si>
-    <t>44019/2021</t>
-  </si>
-  <si>
     <t>21.04.2026</t>
   </si>
   <si>
@@ -789,6 +795,105 @@
     <t>12.03.2026</t>
   </si>
   <si>
+    <t>M.B.</t>
+  </si>
+  <si>
+    <t>35401/2021</t>
+  </si>
+  <si>
+    <t>C.T.</t>
+  </si>
+  <si>
+    <t>42097/2021</t>
+  </si>
+  <si>
+    <t>K.H.</t>
+  </si>
+  <si>
+    <t>37289/2021</t>
+  </si>
+  <si>
+    <t>M.S.</t>
+  </si>
+  <si>
+    <t>36129/2021</t>
+  </si>
+  <si>
+    <t>Z.V.</t>
+  </si>
+  <si>
+    <t>3827/2021</t>
+  </si>
+  <si>
+    <t>40354/2021</t>
+  </si>
+  <si>
+    <t>I.T.</t>
+  </si>
+  <si>
+    <t>40349/2021</t>
+  </si>
+  <si>
+    <t>32528/2021</t>
+  </si>
+  <si>
+    <t>30073/2021</t>
+  </si>
+  <si>
+    <t>P.A.</t>
+  </si>
+  <si>
+    <t>38326/2021</t>
+  </si>
+  <si>
+    <t>V.S.</t>
+  </si>
+  <si>
+    <t>28860/2021</t>
+  </si>
+  <si>
+    <t>F.E.</t>
+  </si>
+  <si>
+    <t>21447/2019</t>
+  </si>
+  <si>
+    <t>B.L.</t>
+  </si>
+  <si>
+    <t>29793/2021</t>
+  </si>
+  <si>
+    <t>S.L.</t>
+  </si>
+  <si>
+    <t>38300/2021</t>
+  </si>
+  <si>
+    <t>N.A.</t>
+  </si>
+  <si>
+    <t>32649/2021</t>
+  </si>
+  <si>
+    <t>P.I.</t>
+  </si>
+  <si>
+    <t>42098/2021</t>
+  </si>
+  <si>
+    <t>T.H.</t>
+  </si>
+  <si>
+    <t>31364/2024</t>
+  </si>
+  <si>
+    <t>K.E.</t>
+  </si>
+  <si>
+    <t>26040/2021</t>
+  </si>
+  <si>
     <t>M.G.</t>
   </si>
   <si>
@@ -813,145 +918,46 @@
     <t>98263/2019</t>
   </si>
   <si>
+    <t>88732/2019</t>
+  </si>
+  <si>
     <t>K.L.</t>
   </si>
   <si>
     <t>26039/2021</t>
   </si>
   <si>
-    <t>K.E.</t>
-  </si>
-  <si>
-    <t>26040/2021</t>
-  </si>
-  <si>
     <t>3260/2023</t>
   </si>
   <si>
+    <t>26052/2021</t>
+  </si>
+  <si>
+    <t>Y.Y.</t>
+  </si>
+  <si>
+    <t>26173/2021</t>
+  </si>
+  <si>
+    <t>I.V.</t>
+  </si>
+  <si>
+    <t>27967/2021</t>
+  </si>
+  <si>
+    <t>Ș.V.</t>
+  </si>
+  <si>
+    <t>69463/2019</t>
+  </si>
+  <si>
+    <t>N.V.</t>
+  </si>
+  <si>
+    <t>26176/2021</t>
+  </si>
+  <si>
     <t>26047/2021</t>
-  </si>
-  <si>
-    <t>26052/2021</t>
-  </si>
-  <si>
-    <t>Y.Y.</t>
-  </si>
-  <si>
-    <t>26173/2021</t>
-  </si>
-  <si>
-    <t>I.V.</t>
-  </si>
-  <si>
-    <t>27967/2021</t>
-  </si>
-  <si>
-    <t>Ș.V.</t>
-  </si>
-  <si>
-    <t>69463/2019</t>
-  </si>
-  <si>
-    <t>P.I.</t>
-  </si>
-  <si>
-    <t>42098/2021</t>
-  </si>
-  <si>
-    <t>N.V.</t>
-  </si>
-  <si>
-    <t>26176/2021</t>
-  </si>
-  <si>
-    <t>88732/2019</t>
-  </si>
-  <si>
-    <t>T.H.</t>
-  </si>
-  <si>
-    <t>31364/2024</t>
-  </si>
-  <si>
-    <t>F.E.</t>
-  </si>
-  <si>
-    <t>21447/2019</t>
-  </si>
-  <si>
-    <t>N.A.</t>
-  </si>
-  <si>
-    <t>32649/2021</t>
-  </si>
-  <si>
-    <t>M.B.</t>
-  </si>
-  <si>
-    <t>35401/2021</t>
-  </si>
-  <si>
-    <t>C.T.</t>
-  </si>
-  <si>
-    <t>42097/2021</t>
-  </si>
-  <si>
-    <t>K.H.</t>
-  </si>
-  <si>
-    <t>37289/2021</t>
-  </si>
-  <si>
-    <t>M.S.</t>
-  </si>
-  <si>
-    <t>36129/2021</t>
-  </si>
-  <si>
-    <t>Z.V.</t>
-  </si>
-  <si>
-    <t>3827/2021</t>
-  </si>
-  <si>
-    <t>40354/2021</t>
-  </si>
-  <si>
-    <t>32528/2021</t>
-  </si>
-  <si>
-    <t>30073/2021</t>
-  </si>
-  <si>
-    <t>P.A.</t>
-  </si>
-  <si>
-    <t>38326/2021</t>
-  </si>
-  <si>
-    <t>V.S.</t>
-  </si>
-  <si>
-    <t>28860/2021</t>
-  </si>
-  <si>
-    <t>I.T.</t>
-  </si>
-  <si>
-    <t>40349/2021</t>
-  </si>
-  <si>
-    <t>B.L.</t>
-  </si>
-  <si>
-    <t>29793/2021</t>
-  </si>
-  <si>
-    <t>S.L.</t>
-  </si>
-  <si>
-    <t>38300/2021</t>
   </si>
   <si>
     <t>05.03.2026</t>
@@ -1363,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1402,13 +1408,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
@@ -1416,13 +1422,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
@@ -1430,13 +1436,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
@@ -1444,10 +1450,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
@@ -1458,13 +1464,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>7</v>
@@ -1472,13 +1478,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
@@ -1486,13 +1492,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>7</v>
@@ -1500,13 +1506,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -1514,13 +1520,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>7</v>
@@ -1528,13 +1534,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
@@ -1542,13 +1548,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>7</v>
@@ -1556,13 +1562,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -1570,13 +1576,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>7</v>
@@ -1584,13 +1590,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
@@ -1598,13 +1604,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>7</v>
@@ -1612,13 +1618,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -1626,13 +1632,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>7</v>
@@ -1640,13 +1646,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
@@ -1654,10 +1660,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>43</v>
@@ -1668,13 +1674,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1682,7 +1688,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>46</v>
@@ -1738,13 +1744,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>7</v>
@@ -1752,13 +1758,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -1766,13 +1772,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>7</v>
@@ -1780,13 +1786,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>7</v>
@@ -1794,13 +1800,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>7</v>
@@ -1808,13 +1814,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
@@ -1822,13 +1828,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>7</v>
@@ -1836,13 +1842,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
@@ -1850,13 +1856,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>7</v>
@@ -1864,13 +1870,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>7</v>
@@ -1878,13 +1884,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>7</v>
@@ -1892,13 +1898,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -1906,13 +1912,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>7</v>
@@ -1920,13 +1926,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>7</v>
@@ -1934,13 +1940,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>7</v>
@@ -1948,13 +1954,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>7</v>
@@ -1962,13 +1968,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>7</v>
@@ -1976,13 +1982,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>7</v>
@@ -1990,13 +1996,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>7</v>
@@ -2004,13 +2010,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
@@ -2018,13 +2024,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>7</v>
@@ -2032,13 +2038,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>7</v>
@@ -2046,13 +2052,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>7</v>
@@ -2060,13 +2066,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>7</v>
@@ -2074,13 +2080,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>7</v>
@@ -2088,13 +2094,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>7</v>
@@ -2102,10 +2108,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>107</v>
@@ -2116,13 +2122,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
@@ -2130,13 +2136,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>7</v>
@@ -2144,10 +2150,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>112</v>
@@ -2158,7 +2164,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>113</v>
@@ -2172,10 +2178,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>115</v>
@@ -2186,7 +2192,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>116</v>
@@ -2200,7 +2206,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>118</v>
@@ -2214,7 +2220,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>120</v>
@@ -2228,7 +2234,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>122</v>
@@ -2242,7 +2248,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>124</v>
@@ -2256,13 +2262,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>7</v>
@@ -2270,13 +2276,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>7</v>
@@ -2284,13 +2290,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>7</v>
@@ -2298,10 +2304,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>132</v>
@@ -2312,13 +2318,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -2326,7 +2332,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>136</v>
@@ -2340,13 +2346,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -2354,13 +2360,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>7</v>
@@ -2368,7 +2374,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>144</v>
@@ -2382,13 +2388,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>7</v>
@@ -2396,13 +2402,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>7</v>
@@ -2410,7 +2416,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>152</v>
@@ -2424,7 +2430,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>154</v>
@@ -2438,7 +2444,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>156</v>
@@ -2452,13 +2458,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>7</v>
@@ -2466,13 +2472,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>7</v>
@@ -2480,13 +2486,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>7</v>
@@ -2494,13 +2500,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>7</v>
@@ -2508,7 +2514,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>170</v>
@@ -2522,7 +2528,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>172</v>
@@ -2536,7 +2542,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>174</v>
@@ -2550,7 +2556,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>176</v>
@@ -2564,7 +2570,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>178</v>
@@ -2578,7 +2584,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>180</v>
@@ -2592,7 +2598,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>182</v>
@@ -2606,7 +2612,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>184</v>
@@ -2620,7 +2626,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>186</v>
@@ -2634,7 +2640,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>188</v>
@@ -2648,7 +2654,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>190</v>
@@ -2662,7 +2668,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>192</v>
@@ -2676,7 +2682,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>194</v>
@@ -2690,13 +2696,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>7</v>
@@ -2704,13 +2710,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>7</v>
@@ -2718,13 +2724,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>7</v>
@@ -2732,13 +2738,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>7</v>
@@ -2746,13 +2752,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>7</v>
@@ -2760,13 +2766,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
@@ -2774,13 +2780,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>7</v>
@@ -2788,13 +2794,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>7</v>
@@ -2802,13 +2808,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>7</v>
@@ -2816,13 +2822,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>7</v>
@@ -2830,13 +2836,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>7</v>
@@ -2844,13 +2850,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>7</v>
@@ -2858,13 +2864,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>7</v>
@@ -2872,13 +2878,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>7</v>
@@ -2886,13 +2892,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>7</v>
@@ -2900,13 +2906,13 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -2914,13 +2920,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>7</v>
@@ -2928,13 +2934,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -2942,10 +2948,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>230</v>
@@ -2956,7 +2962,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>231</v>
@@ -2970,7 +2976,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>233</v>
@@ -2984,7 +2990,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>235</v>
@@ -2998,13 +3004,13 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>7</v>
@@ -3012,13 +3018,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -3026,13 +3032,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>7</v>
@@ -3040,10 +3046,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>243</v>
@@ -3054,13 +3060,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>7</v>
@@ -3068,13 +3074,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>245</v>
+        <v>169</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>7</v>
@@ -3082,13 +3088,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="C123" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>7</v>
@@ -3096,13 +3102,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>7</v>
@@ -3110,13 +3116,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="C125" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>7</v>
@@ -3124,7 +3130,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>257</v>
@@ -3138,7 +3144,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>259</v>
@@ -3152,7 +3158,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>261</v>
@@ -3166,7 +3172,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>263</v>
@@ -3180,7 +3186,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>265</v>
@@ -3194,10 +3200,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>267</v>
@@ -3208,13 +3214,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -3222,13 +3228,13 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>7</v>
@@ -3236,10 +3242,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>270</v>
+        <v>64</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>271</v>
@@ -3250,7 +3256,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>272</v>
@@ -3264,7 +3270,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>274</v>
@@ -3278,7 +3284,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>276</v>
@@ -3292,7 +3298,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>278</v>
@@ -3306,13 +3312,13 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>7</v>
@@ -3320,13 +3326,13 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>7</v>
@@ -3334,13 +3340,13 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>7</v>
@@ -3348,13 +3354,13 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>7</v>
@@ -3362,13 +3368,13 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>7</v>
@@ -3376,13 +3382,13 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>7</v>
@@ -3390,13 +3396,13 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>7</v>
@@ -3404,13 +3410,13 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -3418,13 +3424,13 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>7</v>
@@ -3432,13 +3438,13 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>7</v>
@@ -3446,13 +3452,13 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>34</v>
+        <v>299</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>7</v>
@@ -3460,13 +3466,13 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>7</v>
@@ -3474,13 +3480,13 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>300</v>
+        <v>68</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>7</v>
@@ -3488,13 +3494,13 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>7</v>
@@ -3502,13 +3508,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>7</v>
@@ -3516,13 +3522,13 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>7</v>
@@ -3530,13 +3536,13 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>7</v>
@@ -3544,13 +3550,13 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>310</v>
+        <v>256</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
@@ -3558,10 +3564,10 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>314</v>
@@ -3572,10 +3578,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>315</v>
+        <v>133</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>316</v>
@@ -3586,20 +3592,34 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="C159" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="D159" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="B160" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D160" s="2" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D159"/>
+  <autoFilter ref="A1:D160"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>